--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486945_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486945_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4057</v>
+        <v>9.8889</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0592</v>
+        <v>7.2757</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3465</v>
+        <v>2.6132</v>
       </c>
       <c r="G2" t="n">
         <v>6.4332</v>
@@ -610,13 +610,13 @@
         <v>2.2588</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2328</v>
+        <v>1.2505</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0931</v>
+        <v>1.1234</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1397</v>
+        <v>0.1271</v>
       </c>
       <c r="V2" t="n">
         <v>1.1786</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1921</v>
+        <v>6.9722</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1293</v>
+        <v>3.6209</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0628</v>
+        <v>3.3513</v>
       </c>
       <c r="G3" t="n">
         <v>6.7272</v>
@@ -688,13 +688,13 @@
         <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1262</v>
+        <v>1.9063</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7169</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>1.843</v>
+        <v>1.1316</v>
       </c>
       <c r="V3" t="n">
         <v>1.4189</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7621</v>
+        <v>2.5381</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9320000000000001</v>
+        <v>1.0638</v>
       </c>
       <c r="F4" t="n">
-        <v>1.83</v>
+        <v>1.4743</v>
       </c>
       <c r="G4" t="n">
         <v>1.8329</v>
@@ -766,13 +766,13 @@
         <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1694</v>
+        <v>0.9454</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5461</v>
+        <v>0.6778</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6233</v>
+        <v>0.2675</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2402</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0733</v>
+        <v>1.8393</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1815</v>
+        <v>0.829</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8918</v>
+        <v>1.0103</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4629</v>
@@ -844,13 +844,13 @@
         <v>0.8214</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7764</v>
+        <v>0.5424</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2048</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4284</v>
+        <v>-0.3098</v>
       </c>
       <c r="V5" t="n">
         <v>0.9384</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9884</v>
+        <v>1.2543</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5895</v>
+        <v>0.5113</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5779</v>
+        <v>0.743</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.882</v>
+        <v>0.7816</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7269</v>
+        <v>0.587</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1552</v>
+        <v>0.1946</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.3564</v>
+        <v>0.5656</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.0142</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3422</v>
+        <v>0.5656</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4743</v>
+        <v>0.2161</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2873</v>
+        <v>0.587</v>
       </c>
       <c r="O6" t="n">
-        <v>0.187</v>
+        <v>-0.3709</v>
       </c>
       <c r="P6" t="n">
         <v>0.4107</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6427</v>
+        <v>0.4107</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4598</v>
+        <v>0.062</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9989</v>
+        <v>-0.0543</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4609</v>
+        <v>0.1163</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.096</v>
+        <v>1.2537</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2021</v>
+        <v>-2.2945</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2981</v>
+        <v>3.5483</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3547</v>
+        <v>-0.882</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5601</v>
+        <v>-0.7269</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7947</v>
+        <v>-0.1552</v>
       </c>
       <c r="J7" t="n">
-        <v>1.541</v>
+        <v>-2.3564</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3042</v>
+        <v>-2.0142</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2368</v>
+        <v>-0.3422</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8137</v>
+        <v>1.4743</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2559</v>
+        <v>1.2873</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5579</v>
+        <v>0.187</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.6694</v>
+        <v>0.4107</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.2855</v>
+        <v>-1.2321</v>
       </c>
       <c r="R7" t="n">
-        <v>0.616</v>
+        <v>1.6427</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7126</v>
+        <v>1.7251</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3021</v>
+        <v>1.2939</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4104</v>
+        <v>0.4312</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>K.  BAOKO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7421</v>
+        <v>0.923</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2362</v>
+        <v>-1.3455</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5059</v>
+        <v>2.2685</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7816</v>
+        <v>2.3547</v>
       </c>
       <c r="H8" t="n">
-        <v>0.587</v>
+        <v>1.5601</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1946</v>
+        <v>0.7947</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5656</v>
+        <v>1.541</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.3042</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5656</v>
+        <v>0.2368</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2161</v>
+        <v>0.8137</v>
       </c>
       <c r="N8" t="n">
-        <v>0.587</v>
+        <v>0.2559</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3709</v>
+        <v>0.5579</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4107</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.2855</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4502</v>
+        <v>0.5396</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3294</v>
+        <v>0.1588</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1208</v>
+        <v>0.3808</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3978</v>
+        <v>0.3673</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3379</v>
+        <v>-2.0961</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9401</v>
+        <v>2.4634</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2691</v>
+        <v>2.0477</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5085</v>
+        <v>1.0668</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7606000000000001</v>
+        <v>0.9809</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2911</v>
+        <v>0.9918</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7383</v>
+        <v>0.0584</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5528999999999999</v>
+        <v>0.9334</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0221</v>
+        <v>1.0559</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2298</v>
+        <v>1.0084</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2077</v>
+        <v>0.0475</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.616</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0534</v>
+        <v>-3.2855</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4873</v>
+        <v>0.1328</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0067</v>
+        <v>-0.0427</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4806</v>
+        <v>0.1755</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5089</v>
+        <v>-0.8549</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6463</v>
+        <v>-2.795</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1373</v>
+        <v>1.9401</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0477</v>
+        <v>-2.2691</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0668</v>
+        <v>-1.5085</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9809</v>
+        <v>-0.7606000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9918</v>
+        <v>-2.2911</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0584</v>
+        <v>-1.7383</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9334</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0559</v>
+        <v>0.0221</v>
       </c>
       <c r="N10" t="n">
-        <v>1.0084</v>
+        <v>0.2298</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0475</v>
+        <v>-0.2077</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.616</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-2.0534</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-3.2855</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7435</v>
+        <v>2.0301</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5928</v>
+        <v>1.5495</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1506</v>
+        <v>0.4806</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>L. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7866</v>
+        <v>-1.0475</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7941</v>
+        <v>-1.4243</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0075</v>
+        <v>0.3769</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3216</v>
+        <v>-0.505</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6099</v>
+        <v>-0.8629</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9315</v>
+        <v>0.3579</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1473</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4497</v>
+        <v>-0.6974</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3024</v>
+        <v>0.0789</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4689</v>
+        <v>0.1134</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8398</v>
+        <v>-0.1656</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3709</v>
+        <v>0.2789</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6427</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4374</v>
+        <v>0.2053</v>
       </c>
       <c r="S11" t="n">
-        <v>1.7132</v>
+        <v>0.2789</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4333</v>
+        <v>0.2208</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2798</v>
+        <v>0.0581</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. GARCIA JIMENEZ</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8135</v>
+        <v>-1.3937</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0718</v>
+        <v>-2.4605</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2583</v>
+        <v>1.0668</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.505</v>
+        <v>0.3216</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8629</v>
+        <v>-0.6099</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3579</v>
+        <v>0.9315</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.1473</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6974</v>
+        <v>-1.4497</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0789</v>
+        <v>1.3024</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1134</v>
+        <v>0.4689</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1656</v>
+        <v>0.8398</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2789</v>
+        <v>-0.3709</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8214</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5129</v>
+        <v>1.1061</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5733</v>
+        <v>0.767</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0604</v>
+        <v>0.3391</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>20.7529</v>
+        <v>21.7407</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1035000000000006</v>
+        <v>0.8847999999999989</v>
       </c>
       <c r="F13" t="n">
-        <v>20.8562</v>
+        <v>20.8561</v>
       </c>
       <c r="G13" t="n">
         <v>16.3799</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8964</v>
+        <v>4.896400000000001</v>
       </c>
       <c r="I13" t="n">
         <v>11.4834</v>
@@ -1444,7 +1444,7 @@
         <v>11.8062</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7975999999999996</v>
+        <v>0.7976000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>11.0084</v>
@@ -1453,13 +1453,13 @@
         <v>4.5738</v>
       </c>
       <c r="N13" t="n">
-        <v>4.0988</v>
+        <v>4.098800000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4749999999999998</v>
+        <v>0.4749999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-8.2135</v>
+        <v>-8.213499999999998</v>
       </c>
       <c r="Q13" t="n">
         <v>-21.561</v>
@@ -1468,19 +1468,19 @@
         <v>13.3473</v>
       </c>
       <c r="S13" t="n">
-        <v>9.5313</v>
+        <v>10.5192</v>
       </c>
       <c r="T13" t="n">
-        <v>6.332999999999999</v>
+        <v>7.3212</v>
       </c>
       <c r="U13" t="n">
-        <v>3.1981</v>
+        <v>3.198</v>
       </c>
       <c r="V13" t="n">
         <v>3.055499999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>3.318100000000001</v>
+        <v>3.3181</v>
       </c>
       <c r="X13" t="n">
         <v>-0.2627</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2368</v>
+        <v>2.5272</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6608</v>
+        <v>1.1377</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5761</v>
+        <v>1.3895</v>
       </c>
       <c r="G14" t="n">
         <v>0.6685</v>
@@ -1546,13 +1546,13 @@
         <v>2.6694</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1043</v>
+        <v>-0.6054</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9645</v>
+        <v>0.4415</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8602</v>
+        <v>-1.0468</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1923</v>
+        <v>1.8785</v>
       </c>
       <c r="E15" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.3039</v>
       </c>
       <c r="F15" t="n">
         <v>2.1823</v>
@@ -1624,10 +1624,10 @@
         <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4339</v>
+        <v>0.1201</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2517</v>
+        <v>-0.0621</v>
       </c>
       <c r="U15" t="n">
         <v>0.1822</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6169</v>
+        <v>0.9795</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3233</v>
+        <v>-0.2187</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9402</v>
+        <v>1.1982</v>
       </c>
       <c r="G16" t="n">
         <v>1.0803</v>
@@ -1702,13 +1702,13 @@
         <v>1.0267</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4634</v>
+        <v>-0.1007</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3294</v>
+        <v>-0.2248</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.134</v>
+        <v>0.124</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6831</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1835</v>
+        <v>-1.3927</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.619</v>
       </c>
       <c r="G17" t="n">
         <v>-3.2773</v>
@@ -1780,13 +1780,13 @@
         <v>3.0801</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4592</v>
+        <v>-1.5498</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3257</v>
+        <v>-0.5349</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1335</v>
+        <v>-1.0149</v>
       </c>
       <c r="V17" t="n">
         <v>1.1786</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.247</v>
+        <v>-1.0378</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6785</v>
+        <v>-2.4693</v>
       </c>
       <c r="F18" t="n">
         <v>1.4315</v>
@@ -1858,10 +1858,10 @@
         <v>2.2588</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7478</v>
+        <v>-0.5386</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8409</v>
+        <v>-0.6317</v>
       </c>
       <c r="U18" t="n">
         <v>0.0931</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9807</v>
+        <v>-1.4385</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0123</v>
+        <v>0.3015</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9685</v>
+        <v>-1.7401</v>
       </c>
       <c r="G19" t="n">
         <v>-2.0477</v>
@@ -1936,13 +1936,13 @@
         <v>1.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9597</v>
+        <v>-0.4175</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7169</v>
+        <v>-0.4031</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2428</v>
+        <v>-0.0144</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9883</v>
+        <v>-2.2132</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6039</v>
+        <v>-0.9177</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3845</v>
+        <v>-1.2956</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2654</v>
@@ -2014,13 +2014,13 @@
         <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5176</v>
+        <v>-1.7425</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0464</v>
+        <v>-0.2674</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.5639</v>
+        <v>-1.475</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1897</v>
+        <v>-2.9352</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.6315</v>
+        <v>-4.3177</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4418</v>
+        <v>1.3825</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4024</v>
@@ -2092,13 +2092,13 @@
         <v>2.2588</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7873</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6355</v>
+        <v>-0.3217</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1518</v>
+        <v>-0.211</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7934</v>
+        <v>-5.0114</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7694</v>
+        <v>-3.9786</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.024</v>
+        <v>-1.0328</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6935</v>
@@ -2170,13 +2170,13 @@
         <v>2.0534</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9356</v>
+        <v>-1.1536</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1435</v>
+        <v>-0.3527</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7921</v>
+        <v>-0.8008</v>
       </c>
       <c r="V22" t="n">
         <v>-1.9856</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1369</v>
+        <v>-5.7638</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4234</v>
+        <v>-4.1096</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7134</v>
+        <v>-1.6541</v>
       </c>
       <c r="G23" t="n">
         <v>-5.7024</v>
@@ -2248,13 +2248,13 @@
         <v>2.6694</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6851</v>
+        <v>-0.312</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6278</v>
+        <v>-0.314</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0573</v>
+        <v>0.002</v>
       </c>
       <c r="V23" t="n">
         <v>-2.0082</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.7796</v>
+        <v>-6.2671</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9011</v>
+        <v>-4.5873</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8785</v>
+        <v>-1.6798</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1859</v>
@@ -2326,13 +2326,13 @@
         <v>1.4374</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.5136</v>
+        <v>-2.0011</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8409</v>
+        <v>-0.5271</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.6728</v>
+        <v>-1.474</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-20.7527</v>
+        <v>-20.0555</v>
       </c>
       <c r="E25" t="n">
-        <v>-20.8562</v>
+        <v>-20.8563</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1034999999999993</v>
+        <v>0.8006000000000004</v>
       </c>
       <c r="G25" t="n">
         <v>-16.3798</v>
@@ -2404,13 +2404,13 @@
         <v>21.5609</v>
       </c>
       <c r="S25" t="n">
-        <v>-9.5311</v>
+        <v>-8.8339</v>
       </c>
       <c r="T25" t="n">
         <v>-3.198</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.3331</v>
+        <v>-5.6356</v>
       </c>
       <c r="V25" t="n">
         <v>-3.0554</v>
